--- a/artfynd/A 4384-2022 artfynd.xlsx
+++ b/artfynd/A 4384-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4384-2022 artfynd.xlsx
+++ b/artfynd/A 4384-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,64 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2220658</v>
+        <v>83869645</v>
       </c>
       <c r="B2" t="n">
-        <v>108193</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219711</v>
+        <v>1445</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>300 m S om Sörsjön, Srm</t>
+          <t>Tullgarn, Galgbacken, ostsidan, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>647524.7242177712</v>
+        <v>647442</v>
       </c>
       <c r="R2" t="n">
-        <v>6540184.649527523</v>
+        <v>6540283</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,22 +751,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2009-10-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-03-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2009-10-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-03-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>under äldre gran i nordsluttning nära bergfot</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,42 +770,33 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Mossrik granskog, fuktdrag</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bengt Hallberg</t>
+          <t>Lennart Karlén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Hallberg</t>
+          <t>Lennart Karlén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>69255270</v>
+        <v>69255182</v>
       </c>
       <c r="B3" t="n">
-        <v>95157</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -849,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>647565.9699562391</v>
+        <v>647541</v>
       </c>
       <c r="R3" t="n">
-        <v>6540254.869471479</v>
+        <v>6540295</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -882,19 +860,9 @@
           <t>2018-01-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-01-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -926,19 +894,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>69255247</v>
+        <v>69255193</v>
       </c>
       <c r="B4" t="n">
-        <v>95157</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -969,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>647556.0446088313</v>
+        <v>647554</v>
       </c>
       <c r="R4" t="n">
-        <v>6540271.001750859</v>
+        <v>6540281</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1002,19 +965,9 @@
           <t>2018-01-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-01-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1046,19 +999,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>69255257</v>
+        <v>69255247</v>
       </c>
       <c r="B5" t="n">
-        <v>95157</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97776</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1089,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>647561.9209102205</v>
+        <v>647556</v>
       </c>
       <c r="R5" t="n">
-        <v>6540266.067021186</v>
+        <v>6540271</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1122,19 +1070,9 @@
           <t>2018-01-26</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2018-01-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1166,64 +1104,51 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>83869645</v>
+        <v>69255257</v>
       </c>
       <c r="B6" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97776</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1445</v>
+        <v>1590</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Dunmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Trichocolea tomentella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ehrh.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tullgarn, Galgbacken, ostsidan, Srm</t>
+          <t>Sörsjön, S om sydspetsen, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>647442.3810716274</v>
+        <v>647562</v>
       </c>
       <c r="R6" t="n">
-        <v>6540282.634036883</v>
+        <v>6540266</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1247,27 +1172,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-03-26</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-01-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-03-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-01-26</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>under äldre gran i nordsluttning nära bergfot</t>
+          <t>Utmed ett stråk med källpåverkad mark strax nedanför sluttning.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1276,76 +1191,69 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lennart Karlén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lennart Karlén</t>
+          <t>Bo Törnquist, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>86933681</v>
+        <v>69255270</v>
       </c>
       <c r="B7" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97776</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>1590</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dunmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Trichocolea tomentella</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ehrh.) Dumort.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tullgarns naturreservat, vägen mot Sörsjön, Srm</t>
+          <t>Sörsjön, S om sydspetsen, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>647602.0058756388</v>
+        <v>647566</v>
       </c>
       <c r="R7" t="n">
-        <v>6540258.834458509</v>
+        <v>6540255</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1369,22 +1277,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-07-17</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-01-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-07-17</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-01-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Utmed ett stråk med källpåverkad mark strax nedanför sluttning.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1393,73 +1296,66 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anton Johansson</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anton Johansson</t>
+          <t>Bo Törnquist, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>87156068</v>
+        <v>72088271</v>
       </c>
       <c r="B8" t="n">
-        <v>108194</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97776</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219711</v>
+        <v>1590</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Dunmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Trichocolea tomentella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ehrh.) Dumort.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sörsjön, S om, Srm</t>
+          <t>Sörsjön, S om sydspetsen, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>647567.2583082593</v>
+        <v>647511</v>
       </c>
       <c r="R8" t="n">
-        <v>6540234.792906059</v>
+        <v>6540309</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1486,22 +1382,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-07-24</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-07-24</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>I kanten av dike från källa. Förekommer på flera ställen utmed den källpåverkade marken nedanför sluttningen. Länsstyrelsen planerar att slutavverka angränsande granskog för att skapa slåtterkärr-rikkärr.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1522,10 +1413,1259 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>94575716</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97776</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1590</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dunmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Trichocolea tomentella</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ehrh.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tullgarn, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>647550</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6540286</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hölö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-04-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-04-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>enstaka skott</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sara Lundkvist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sara Lundkvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100097749</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97776</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1590</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dunmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Trichocolea tomentella</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ehrh.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tullgarn, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>647533</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6540289</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hölö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-04-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-04-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>71645274</v>
+      </c>
+      <c r="B11" t="n">
+        <v>96338</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sörsjön, S om, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>647521</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6540287</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hölö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2018-05-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2018-05-29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Vid kanten av källpåverkad bäck, strax öster om källa.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2220658</v>
+      </c>
+      <c r="B12" t="n">
+        <v>111390</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>300 m S om Sörsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>647525</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6540185</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hölö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2009-10-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2009-10-18</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Mossrik granskog, fuktdrag</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Bengt Hallberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Bengt Hallberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>60162625</v>
+      </c>
+      <c r="B13" t="n">
+        <v>111390</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sörsjön, sumpskog S om, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>647570</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6540298</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hölö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2016-06-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2016-06-07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>87156068</v>
+      </c>
+      <c r="B14" t="n">
+        <v>111390</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sörsjön, S om, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>647567</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6540235</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hölö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2020-07-24</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2020-07-24</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
           <t>Bo Törnquist, Bo Karlsson</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>69255222</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99141</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sörsjön, S om sydspetsen, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>647563</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6540281</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hölö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2018-01-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2018-01-26</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Källpåverkad sumpskog.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>60570723</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Tullgarn, Sörsjön nära badplatsens parkering, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>647630</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6540181</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hölö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2016-07-14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2016-07-14</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>69247982</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sörsjön 200 m sso, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>647621</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6540211</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hölö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2018-01-26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2018-01-26</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Bo Karlsson, Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>69255330</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sörsjön, S om sydspetsen, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>647637</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6540219</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hölö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2018-01-26</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2018-01-26</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>86933681</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Tullgarns naturreservat, vägen mot Sörsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>647602</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6540259</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hölö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2020-07-17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2020-07-17</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anton Johansson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anton Johansson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>6221677</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>150 m S Sörsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>647503</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6540304</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hölö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2009-08-03</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2009-08-03</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Granskog, surdrag</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Bengt Hallberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Bengt Hallberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4384-2022 artfynd.xlsx
+++ b/artfynd/A 4384-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83869645</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69255182</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69255193</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,6 +1121,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69255247</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1206,6 +1231,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69255257</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1311,6 +1341,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69255270</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1417,6 +1452,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72088271</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1519,6 +1559,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94575716</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1616,6 +1661,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100097749</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1721,6 +1771,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71645274</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1837,6 +1892,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2220658</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1939,6 +1999,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60162625</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2041,6 +2106,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87156068</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2146,6 +2216,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69255222</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2248,6 +2323,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60570723</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2366,6 +2446,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69247982</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2466,6 +2551,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69255330</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2568,6 +2658,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86933681</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2666,8 +2761,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6221677</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>